--- a/mod_project/data_tables/qol_joint_skill_text.xlsx
+++ b/mod_project/data_tables/qol_joint_skill_text.xlsx
@@ -834,11 +834,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies. 100% chance of causing sleep.</t>
+          <t>Deal non-elemental damage to all enemies. 100% chance of sleep.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -940,11 +940,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage and lower DEF and magic defense (-20%) for all enemies.</t>
+          <t>Non-elemental damage to all enemies. DEF and magic defense -20%.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Activate Circle Brave (+16%), Circle Protect (+16%) and Moon Curtain (+25%) at once.</t>
+          <t>Circle Brave (+16%), Circle Protect (+16%) and Moon Curtain (+25%).</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1152,11 +1152,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deal damage with an 85% chance to silence/freeze. Pierces to the back row.</t>
+          <t>Deal damage through to the back row. 85% chance to silence/freeze.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -1205,11 +1205,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Form up to increase speed (+50%) and physical accuracy (+75%) for all allies.</t>
+          <t>Form up: speed +50% and physical accuracy +75% for all allies.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -1417,11 +1417,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deal damage and reduce physical attack/defense (-25%). Pierces to the back row.</t>
+          <t>Deal damage through to the back row. Physical attack/defense -25%.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deal physical damage, with a 90% chance to delay the target's next turn.</t>
+          <t>Deal physical damage. 90% chance to delay the target's next turn.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -1735,11 +1735,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Deal physical damage to one enemy. 100% chance of poison/paralysis/sleep.</t>
+          <t>Physical damage to one enemy. 100% chance of poison/paralysis/sleep.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Waste one enemy and poison the target (100%) with a rare gun-type weapon.</t>
+          <t>Waste one enemy and poison it (100%) with a rare gun.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cancel all enemy chants, dances, songs, and dolls with a superior performance.</t>
+          <t>Cancel enemy chants, dances, songs and dolls by outperforming them.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Slice a random enemy 2-5 times with the power of friendship. And swords.</t>
+          <t>Slice a random enemy 2-5 times with friendship power. And swords.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rough up (4 hits) and poison (100%) one enemy with the power of darkness.</t>
+          <t>Rough up (4 hits) and poison (100%) one enemy with dark power.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fire two arrows of light that pierce to the back row and may silence (50%).</t>
+          <t>Two arrows of light pierce to the back row and may silence (50%).</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -2583,11 +2583,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>The deadly Maid Beam pierces to the back row and begins petrifying targets (75%).</t>
+          <t>The deadly Maid Beam pierces to the back row. Petrifying (75%).</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Heal the party to full HP and remove debuffs and ailments with a secret potion.</t>
+          <t>A secret potion: full HP for the party, debuffs and ailments removed.</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -2795,11 +2795,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hurl 5% of your wallet at one enemy for up to 10000 damage. (You won't get it back.)</t>
+          <t>Hurl 5% of your wallet at one enemy (max 10000 damage). No refunds.</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -2848,11 +2848,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dish out paralysis (50%) and 7 times the user's level in damage to all enemies.</t>
+          <t>Dish out paralysis (50%) and 7x user level damage to all enemies.</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -2901,11 +2901,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gain 4x the current enemies' value in gold at the end of battle. (Min. 100)</t>
+          <t>Gain 4x the enemies' gold value at the end of battle. (Min. 100)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -3007,11 +3007,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Waste one enemy and lower target's phys. DEF (-35%) with a rare gun-type weapon.</t>
+          <t>Waste one enemy and lower its phys. DEF (-35%) with a rare gun.</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -3113,11 +3113,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Deal 77 times the user's level in damage to one enemy. Jokers are wild!</t>
+          <t>Deal 77x the user's level in damage to one enemy. Jokers are wild!</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Deal damage and likely petrify all enemies by tugging their heartstrings.</t>
+          <t>Damage and likely petrify all enemies by tugging their heartstrings.</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>With three firearms in your hands, rain lead upon your enemies at random (9 hits).</t>
+          <t>Three firearms in hand, rain lead on random enemies (9 hits).</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>

--- a/mod_project/data_tables/qol_joint_skill_text.xlsx
+++ b/mod_project/data_tables/qol_joint_skill_text.xlsx
@@ -1046,11 +1046,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Circle Brave (+16%), Circle Protect (+16%) and Moon Curtain (+25%).</t>
+          <t>Circle Brave (+16%), Circle Protect (+16%) and Moon Curtain (+25).</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>

--- a/mod_project/data_tables/qol_joint_skill_text.xlsx
+++ b/mod_project/data_tables/qol_joint_skill_text.xlsx
@@ -516,11 +516,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deal physical damage to an enemy row with the party's front three.</t>
+          <t>Physical damage to an enemy row. [1/7 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inflict a powerful physical attack on one enemy. Inflicts slow (100%).</t>
+          <t>Powerful physical attack. Inflicts slow (100%). [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deal physical damage to one enemy and increase equipment drop rate.</t>
+          <t>Physical damage to an enemy; drop rate UP. [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rain arrows down upon all enemies across 4 turns.</t>
+          <t>Rain arrows down on all foes across 4 turns. [1/3 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -728,11 +728,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fully restore the party's HP and dispel all status ailments.</t>
+          <t>Fully restore party HP, dispel status ailments. [1/5 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -781,11 +781,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deal physical damage to an enemy row. 85% chance of instakill.</t>
+          <t>Physical damage to an enemy row. 85% instakill. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -834,11 +834,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies. 100% chance of sleep.</t>
+          <t>Non-elemental damage to all foes. 100% sleep. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Inflict one enemy with 3-5 bash attacks. 85% chance of stun.</t>
+          <t>3-5 bash attacks on one enemy. 85% stun. [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -940,11 +940,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-elemental damage to all enemies. DEF and magic defense -20%.</t>
+          <t>Non-elem dmg to all foes. DEF &amp; magic DEF -20%. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -993,11 +993,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deal physical damage and 1-5 defense-piercing attacks on one enemy.</t>
+          <t>Physical and 1-5 piercing attacks on one foe. [1/2 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Circle Brave (+16%), Circle Protect (+16%) and Moon Curtain (+25).</t>
+          <t>Circle Brave/Protect (+16%), Moon Curtain (+25). [1/5 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1099,11 +1099,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cut an enemy row's HP to 25% (ineffective vs. bosses).</t>
+          <t>Cut enemy row's HP to 25% (no boss effect). [1/3 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1152,11 +1152,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deal damage through to the back row. 85% chance to silence/freeze.</t>
+          <t>Damage to back row. 85% silence/freeze. [1/3 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -1205,11 +1205,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Form up: speed +50% and physical accuracy +75% for all allies.</t>
+          <t>Party speed +50% and physical accuracy +75%. [1/7 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Inflict 2,000 direct damage to all enemies and dispel their buffs.</t>
+          <t>2,000 direct damage to all foes, dispel buffs. [1/3 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -1311,11 +1311,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Increase magic attack (+50%) and critical rate (+20%) for all allies.</t>
+          <t>Allies magic ATK (+50%) and crit rate (+20%). [1/4 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -1364,11 +1364,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>See the stats of all enemies.</t>
+          <t>See the stats of all enemies. [1/9 TP, 3 Pep]</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -1417,11 +1417,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deal damage through to the back row. Physical attack/defense -25%.</t>
+          <t>Damage to back row. Phys attack/defense -25%. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -1470,11 +1470,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Attack an enemy 7 times with vigor... and questionable accuracy.</t>
+          <t>Attack an enemy 7 times with wild accuracy. [1/3 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -1523,11 +1523,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Attack all enemies twice.</t>
+          <t>Attack all enemies twice. [1/4 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -1576,11 +1576,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Inflict a wind attack against all enemies. 90% chance of paralysis.</t>
+          <t>Wind attack to all foes. 90% paralysis. [1/5 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1629,11 +1629,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deal physical damage. 90% chance to delay the target's next turn.</t>
+          <t>Physical damage. 90% turn delay chance. [1/7 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -1682,11 +1682,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deal physical damage and use Shadow Sew (100%) against an enemy row.</t>
+          <t>Physical damage &amp; Shadow Sew (100%) on a row. [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -1735,11 +1735,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Physical damage to one enemy. 100% chance of poison/paralysis/sleep.</t>
+          <t>Physical damage. 100% poison/paralyze/sleep. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1788,11 +1788,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>All allies perform the Shadow Clone technique.</t>
+          <t>All allies perform Shadow Clone technique. [1/4 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -1841,11 +1841,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Increase Pep (+15) for the ally whose Pep is the lowest.</t>
+          <t>Pep +15 for the ally with the lowest Pep. [1/7 TP, 1 Pep]</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -1894,11 +1894,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Perform a critical attack on all enemies with 100% accuracy.</t>
+          <t>Critical attack on all enemies with 100% hit. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -1947,11 +1947,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Inflict 0-4 bash attacks on an enemy row.</t>
+          <t>0-4 bash attacks on an enemy row. [1/3 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Attack one enemy (2x damage to Undead, Demons, and Apparitions).</t>
+          <t>Attack one foe (2x vs Undead/Demon/Apparition). [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wind up your weapons and hit an enemy row from both sides at once.</t>
+          <t>Strike an enemy row from both sides at once. [1/7 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Spiral into the enemy formation for a penetrating attack.</t>
+          <t>Spiral into enemy ranks for a piercing attack. [1/7 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Waste one enemy and poison it (100%) with a rare gun.</t>
+          <t>Waste one enemy and poison it (100%). [1/5 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cancel enemy chants, dances, songs and dolls by outperforming them.</t>
+          <t>Cancel enemy chants, dances, songs and dolls. [1/7 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -2318,11 +2318,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Dogpile one enemy with attacks from three allies in a row.</t>
+          <t>Dogpile an enemy with three allies in a row. [1/4 TP, 8 Pep]</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Slice a random enemy 2-5 times with friendship power. And swords.</t>
+          <t>Slice a foe 2-5 times with friendship &amp; swords. [1/4 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rough up (4 hits) and poison (100%) one enemy with dark power.</t>
+          <t>Rough up (4 hits) and poison (100%) one foe. [1/3 TP, 12 Pep]</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -2477,11 +2477,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pummel one enemy. 2x damage to Undead, Demons, and Apparitions.</t>
+          <t>Pummel one foe (2x vs Undead/Demon/Apparition). [1/5 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Two arrows of light pierce to the back row and may silence (50%).</t>
+          <t>Two light arrows pierce back row; silence (50%). [1/5 TP, 12 Pep]</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>The deadly Maid Beam pierces to the back row. Petrifying (75%).</t>
+          <t>Deadly Maid Beam pierces back row. Petrify (75%). [1/4 TP, 8 Pep]</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -2636,11 +2636,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lull all enemies to sleep with hypnosis. Huge chance of success.</t>
+          <t>Lull all enemies to sleep with hypnosis. [1/5 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -2689,11 +2689,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A secret potion: full HP for the party, debuffs and ailments removed.</t>
+          <t>Full party HP; dispel debuffs &amp; ailments. [1/7 TP, 8 Pep]</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -2742,11 +2742,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Immolate all enemies and absorb their HP and TP (damage cap 5000).</t>
+          <t>Immolate foes, absorb HP/TP (5000 dmg cap). [1/4 TP, 30 Pep]</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -2795,11 +2795,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hurl 5% of your wallet at one enemy (max 10000 damage). No refunds.</t>
+          <t>Hurl 5% wallet at one foe (max 10000 dmg). [1/3 TP, 20 Pep]</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -2848,11 +2848,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dish out paralysis (50%) and 7x user level damage to all enemies.</t>
+          <t>Paralysis (50%) and 7x Lv dmg to all foes. [1/5 TP, 6 Pep]</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -2901,11 +2901,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gain 4x the enemies' gold value at the end of battle. (Min. 100)</t>
+          <t>Gain 4x enemies' gold after battle (min 100). [1/7 TP, 20 Pep]</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -2954,11 +2954,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Instakill one random combatant, friend or foe.</t>
+          <t>Instakill one random combatant, friend or foe. [1/9 TP, 8 Pep]</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -3007,11 +3007,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Waste one enemy and lower its phys. DEF (-35%) with a rare gun.</t>
+          <t>Waste one enemy and lower phys. DEF (-35%). [1/4 TP, 12 Pep]</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Summon the goddess of life to resurrect all allies (HP 100%).</t>
+          <t>Goddess of life resurrects allies (HP 100%). [1/4 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3113,11 +3113,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Deal 77x the user's level in damage to one enemy. Jokers are wild!</t>
+          <t>Deal 77x user Lv in dmg to a foe. Wild jokers! [All TP, 50 Pep]</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Damage and likely petrify all enemies by tugging their heartstrings.</t>
+          <t>Damage and likely petrify all enemies. [1/4 TP, 30 Pep]</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -3219,11 +3219,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Three firearms in hand, rain lead on random enemies (9 hits).</t>
+          <t>Three guns rain lead on random foes (9 hits). [1/5 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
